--- a/資料表規劃/260307.xlsx
+++ b/資料表規劃/260307.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csiyu\Desktop\ntubimd115208\資料表規劃\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CD637E7-5A89-4399-BF03-FBAF8CFBE618}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8397EC-4F39-4024-BFAF-3CD646088CF1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16185" windowHeight="5820" xr2:uid="{E480683D-8966-47B7-B0F2-886B39555ABC}"/>
   </bookViews>
@@ -498,9 +498,6 @@
     <t>尿蛋白</t>
   </si>
   <si>
-    <t>varchar(2000)</t>
-  </si>
-  <si>
     <t>disease_id</t>
   </si>
   <si>
@@ -571,6 +568,10 @@
   </si>
   <si>
     <t>雞蛋、牛奶、花生、海鮮、堅果和小麥</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>text</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -1110,7 +1111,7 @@
   <dimension ref="A1:AF1002"/>
   <sheetFormatPr defaultColWidth="21.73046875" defaultRowHeight="16.149999999999999"/>
   <sheetData>
-    <row r="1" spans="1:32" ht="76.5">
+    <row r="1" spans="1:32" ht="25.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1234,7 +1235,7 @@
       <c r="AE3" s="1"/>
       <c r="AF3" s="1"/>
     </row>
-    <row r="4" spans="1:32" ht="25.5">
+    <row r="4" spans="1:32">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -1316,7 +1317,7 @@
       <c r="AE4" s="1"/>
       <c r="AF4" s="1"/>
     </row>
-    <row r="5" spans="1:32" ht="38.25">
+    <row r="5" spans="1:32">
       <c r="A5" s="7" t="s">
         <v>15</v>
       </c>
@@ -1398,7 +1399,7 @@
       <c r="AE5" s="1"/>
       <c r="AF5" s="1"/>
     </row>
-    <row r="6" spans="1:32" ht="25.5">
+    <row r="6" spans="1:32">
       <c r="A6" s="8" t="s">
         <v>30</v>
       </c>
@@ -1480,7 +1481,7 @@
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:32" ht="38.25">
+    <row r="7" spans="1:32">
       <c r="A7" s="14" t="s">
         <v>42</v>
       </c>
@@ -1562,7 +1563,7 @@
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:32" ht="38.25">
+    <row r="8" spans="1:32">
       <c r="A8" s="8" t="s">
         <v>56</v>
       </c>
@@ -1644,7 +1645,7 @@
       <c r="AE8" s="1"/>
       <c r="AF8" s="1"/>
     </row>
-    <row r="9" spans="1:32" ht="25.5">
+    <row r="9" spans="1:32">
       <c r="A9" s="14" t="s">
         <v>70</v>
       </c>
@@ -1706,7 +1707,7 @@
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
     </row>
-    <row r="10" spans="1:32" ht="25.5">
+    <row r="10" spans="1:32">
       <c r="A10" s="8" t="s">
         <v>63</v>
       </c>
@@ -1770,7 +1771,7 @@
       <c r="AE10" s="1"/>
       <c r="AF10" s="1"/>
     </row>
-    <row r="11" spans="1:32" ht="25.5">
+    <row r="11" spans="1:32">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -1826,7 +1827,7 @@
       <c r="AE11" s="1"/>
       <c r="AF11" s="1"/>
     </row>
-    <row r="12" spans="1:32" ht="25.5">
+    <row r="12" spans="1:32">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1882,7 +1883,7 @@
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
     </row>
-    <row r="13" spans="1:32" ht="38.25">
+    <row r="13" spans="1:32">
       <c r="A13" s="3" t="s">
         <v>11</v>
       </c>
@@ -1944,7 +1945,7 @@
       <c r="AE13" s="1"/>
       <c r="AF13" s="1"/>
     </row>
-    <row r="14" spans="1:32" ht="38.25">
+    <row r="14" spans="1:32">
       <c r="A14" s="7" t="s">
         <v>105</v>
       </c>
@@ -2010,7 +2011,7 @@
       <c r="AE14" s="1"/>
       <c r="AF14" s="1"/>
     </row>
-    <row r="15" spans="1:32" ht="89.25">
+    <row r="15" spans="1:32" ht="38.25">
       <c r="A15" s="8" t="s">
         <v>112</v>
       </c>
@@ -2074,7 +2075,7 @@
       <c r="AE15" s="1"/>
       <c r="AF15" s="1"/>
     </row>
-    <row r="16" spans="1:32" ht="38.25">
+    <row r="16" spans="1:32">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -2128,7 +2129,7 @@
     </row>
     <row r="17" spans="1:32" ht="30.75">
       <c r="A17" s="21" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -2188,7 +2189,7 @@
       <c r="AE17" s="1"/>
       <c r="AF17" s="1"/>
     </row>
-    <row r="18" spans="1:32" ht="60">
+    <row r="18" spans="1:32" ht="30">
       <c r="A18" s="19" t="s">
         <v>127</v>
       </c>
@@ -2248,7 +2249,7 @@
       <c r="AE18" s="1"/>
       <c r="AF18" s="1"/>
     </row>
-    <row r="19" spans="1:32" ht="25.5">
+    <row r="19" spans="1:32">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -2306,7 +2307,7 @@
       <c r="AE19" s="1"/>
       <c r="AF19" s="1"/>
     </row>
-    <row r="20" spans="1:32" ht="38.25">
+    <row r="20" spans="1:32" ht="25.5">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2358,7 +2359,7 @@
       <c r="AE20" s="1"/>
       <c r="AF20" s="1"/>
     </row>
-    <row r="21" spans="1:32" ht="63.75">
+    <row r="21" spans="1:32" ht="25.5">
       <c r="A21" s="3" t="s">
         <v>11</v>
       </c>
@@ -2416,7 +2417,7 @@
       <c r="AE21" s="1"/>
       <c r="AF21" s="1"/>
     </row>
-    <row r="22" spans="1:32" ht="25.5">
+    <row r="22" spans="1:32">
       <c r="A22" s="7" t="s">
         <v>103</v>
       </c>
@@ -2466,7 +2467,7 @@
       <c r="AE22" s="1"/>
       <c r="AF22" s="1"/>
     </row>
-    <row r="23" spans="1:32" ht="25.5">
+    <row r="23" spans="1:32">
       <c r="A23" s="9" t="s">
         <v>15</v>
       </c>
@@ -2524,7 +2525,7 @@
       <c r="AE23" s="1"/>
       <c r="AF23" s="1"/>
     </row>
-    <row r="24" spans="1:32" ht="38.25">
+    <row r="24" spans="1:32">
       <c r="A24" s="15" t="s">
         <v>105</v>
       </c>
@@ -2588,7 +2589,7 @@
       <c r="AE24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:32" ht="38.25">
+    <row r="25" spans="1:32">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -2644,7 +2645,7 @@
       <c r="AE25" s="1"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:32" ht="51">
+    <row r="26" spans="1:32" ht="25.5">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2702,7 +2703,7 @@
       <c r="AE26" s="1"/>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:32" ht="51">
+    <row r="27" spans="1:32" ht="25.5">
       <c r="A27" s="3" t="s">
         <v>11</v>
       </c>
@@ -2749,7 +2750,7 @@
         <v>121</v>
       </c>
       <c r="V27" s="8" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="W27" s="8" t="s">
         <v>32</v>
@@ -2766,9 +2767,9 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:32" ht="38.25">
+    <row r="28" spans="1:32" ht="25.5">
       <c r="A28" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>20</v>
@@ -2777,18 +2778,18 @@
         <v>17</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>160</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>161</v>
       </c>
       <c r="H28" s="17"/>
       <c r="I28" s="14" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="8" t="s">
@@ -2830,9 +2831,9 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:32" ht="25.5">
+    <row r="29" spans="1:32">
       <c r="A29" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>43</v>
@@ -2841,7 +2842,7 @@
         <v>32</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
@@ -2880,7 +2881,7 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:32" ht="25.5">
+    <row r="30" spans="1:32">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2890,7 +2891,7 @@
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
       <c r="I30" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J30" s="1"/>
       <c r="K30" s="8" t="s">
@@ -2901,7 +2902,7 @@
       </c>
       <c r="M30" s="18"/>
       <c r="N30" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
@@ -2922,7 +2923,7 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:32" ht="25.5">
+    <row r="31" spans="1:32">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2972,16 +2973,16 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:32" ht="25.5">
+    <row r="32" spans="1:32">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="D32" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G32" s="7" t="s">
         <v>20</v>
@@ -2990,7 +2991,7 @@
         <v>17</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
@@ -3016,7 +3017,7 @@
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" ht="25.5">
+    <row r="33" spans="1:32">
       <c r="A33" s="3" t="s">
         <v>11</v>
       </c>
@@ -3031,7 +3032,7 @@
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G33" s="8" t="s">
         <v>20</v>
@@ -3040,7 +3041,7 @@
         <v>35</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
@@ -3066,9 +3067,9 @@
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="25.5">
+    <row r="34" spans="1:32">
       <c r="A34" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>20</v>
@@ -3077,7 +3078,7 @@
         <v>17</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
@@ -3108,7 +3109,7 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="35" spans="1:32" ht="25.5">
+    <row r="35" spans="1:32">
       <c r="A35" s="9" t="s">
         <v>15</v>
       </c>
@@ -3150,9 +3151,9 @@
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
     </row>
-    <row r="36" spans="1:32" ht="25.5">
+    <row r="36" spans="1:32">
       <c r="A36" s="15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B36" s="15" t="s">
         <v>20</v>
@@ -3161,14 +3162,14 @@
         <v>35</v>
       </c>
       <c r="D36" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E36" s="1"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
@@ -3194,7 +3195,7 @@
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
     </row>
-    <row r="37" spans="1:32" ht="25.5">
+    <row r="37" spans="1:32">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -3236,7 +3237,7 @@
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="25.5">
+    <row r="38" spans="1:32">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -3285,7 +3286,7 @@
       <c r="D39" s="2"/>
       <c r="E39" s="1"/>
       <c r="F39" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G39" s="9" t="s">
         <v>20</v>
@@ -3294,7 +3295,7 @@
         <v>34</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="2"/>
@@ -3320,7 +3321,7 @@
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
     </row>
-    <row r="40" spans="1:32" ht="25.5">
+    <row r="40" spans="1:32">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -3396,7 +3397,7 @@
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
     </row>
-    <row r="42" spans="1:32" ht="25.5">
+    <row r="42" spans="1:32">
       <c r="A42" s="3" t="s">
         <v>11</v>
       </c>
@@ -3438,9 +3439,9 @@
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
     </row>
-    <row r="43" spans="1:32" ht="25.5">
+    <row r="43" spans="1:32">
       <c r="A43" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>20</v>
@@ -3478,7 +3479,7 @@
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
     </row>
-    <row r="44" spans="1:32" ht="25.5">
+    <row r="44" spans="1:32">
       <c r="A44" s="9" t="s">
         <v>15</v>
       </c>
@@ -3496,7 +3497,7 @@
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
@@ -3522,7 +3523,7 @@
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
     </row>
-    <row r="45" spans="1:32" ht="25.5">
+    <row r="45" spans="1:32">
       <c r="A45" s="15" t="s">
         <v>22</v>
       </c>
@@ -3572,14 +3573,14 @@
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
     </row>
-    <row r="46" spans="1:32" ht="38.25">
+    <row r="46" spans="1:32">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="1"/>
       <c r="F46" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>20</v>
@@ -3588,7 +3589,7 @@
         <v>17</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
@@ -3614,14 +3615,14 @@
       <c r="AE46" s="1"/>
       <c r="AF46" s="1"/>
     </row>
-    <row r="47" spans="1:32" ht="38.25">
+    <row r="47" spans="1:32">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="1"/>
       <c r="F47" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G47" s="8" t="s">
         <v>20</v>
@@ -3630,7 +3631,7 @@
         <v>35</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
@@ -3734,7 +3735,7 @@
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J50" s="1"/>
       <c r="K50" s="2"/>
@@ -3760,7 +3761,7 @@
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
     </row>
-    <row r="51" spans="1:32" ht="25.5">
+    <row r="51" spans="1:32">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -3802,7 +3803,7 @@
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
     </row>
-    <row r="52" spans="1:32" ht="38.25">
+    <row r="52" spans="1:32">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -3844,14 +3845,14 @@
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
     </row>
-    <row r="53" spans="1:32" ht="38.25">
+    <row r="53" spans="1:32">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="1"/>
       <c r="F53" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>20</v>
@@ -3860,7 +3861,7 @@
         <v>34</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="2"/>
@@ -3886,7 +3887,7 @@
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
     </row>
-    <row r="54" spans="1:32" ht="25.5">
+    <row r="54" spans="1:32">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
